--- a/data/design_scope.xlsx
+++ b/data/design_scope.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\asp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE316F4-2C45-4BB3-B7B9-CD1880620C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A7C736-144C-49B6-8B2D-01E4666378C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A3A8F8E-73CB-41C2-ABCC-74354089770C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A3A8F8E-73CB-41C2-ABCC-74354089770C}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Scope " sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="168">
   <si>
     <t>Temporary Works design excluded from scope</t>
   </si>
@@ -543,9 +543,6 @@
   </si>
   <si>
     <t>Arup Comments</t>
-  </si>
-  <si>
-    <t>ASP4 Design Scope</t>
   </si>
 </sst>
 </file>
@@ -611,7 +608,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -633,12 +630,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF225A40"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -731,19 +722,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -755,26 +734,31 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1110,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A277FA1E-8462-4DA9-9D7E-1052A60AF1E3}">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
@@ -1121,112 +1105,114 @@
     <col min="6" max="6" width="223" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="25" t="s">
+    <row r="1" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="18" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
+    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-    </row>
-    <row r="4" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="18" t="s">
-        <v>161</v>
-      </c>
+      <c r="A3" s="19"/>
+      <c r="B3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
       <c r="B4" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="19"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+      <c r="A5" s="19"/>
       <c r="B5" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>152</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1234,9 +1220,9 @@
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1244,9 +1230,9 @@
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1254,9 +1240,9 @@
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1264,59 +1250,69 @@
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2"/>
+      <c r="E13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>142</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="F16" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="3" t="s">
         <v>134</v>
@@ -1326,159 +1322,151 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>135</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3"/>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="2"/>
+      <c r="A21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="12"/>
     </row>
     <row r="22" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
+      <c r="A22" s="20" t="s">
+        <v>61</v>
+      </c>
       <c r="B22" s="2" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3"/>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="16"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="A24" s="20"/>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>80</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="2"/>
+      <c r="E25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
+      <c r="A26" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="3"/>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>56</v>
-      </c>
+      <c r="A28" s="20"/>
       <c r="B28" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="3"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="3"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
+      <c r="A30" s="20"/>
       <c r="B30" s="2" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1486,21 +1474,19 @@
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>120</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="3"/>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
+      <c r="A32" s="20"/>
       <c r="B32" s="2" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1508,9 +1494,9 @@
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="2" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1518,19 +1504,23 @@
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
+      <c r="A34" s="20"/>
       <c r="B34" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="2"/>
+      <c r="E34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
+      <c r="A35" s="20"/>
       <c r="B35" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1538,23 +1528,21 @@
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="2"/>
     </row>
     <row r="37" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
+      <c r="A37" s="20"/>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1562,31 +1550,31 @@
       <c r="F37" s="2"/>
     </row>
     <row r="38" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
+      <c r="A38" s="20"/>
       <c r="B38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="3"/>
       <c r="F38" s="2"/>
     </row>
     <row r="39" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
+      <c r="A39" s="20"/>
       <c r="B39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="3"/>
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
+      <c r="A40" s="20"/>
       <c r="B40" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -1594,9 +1582,9 @@
       <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
+      <c r="A41" s="20"/>
       <c r="B41" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>76</v>
@@ -1606,9 +1594,9 @@
       <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
+      <c r="A42" s="20"/>
       <c r="B42" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -1616,143 +1604,153 @@
       <c r="F42" s="2"/>
     </row>
     <row r="43" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
+      <c r="A43" s="20"/>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3"/>
       <c r="F43" s="2"/>
     </row>
     <row r="44" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
+      <c r="A44" s="20"/>
       <c r="B44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="2"/>
+      <c r="E44" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="45" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
+      <c r="A45" s="20" t="s">
+        <v>40</v>
+      </c>
       <c r="B45" s="2" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="3"/>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
+      <c r="A46" s="20"/>
       <c r="B46" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>40</v>
-      </c>
+      <c r="A47" s="20"/>
       <c r="B47" s="2" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D47" s="2"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="2"/>
+      <c r="E47" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
+      <c r="A48" s="20"/>
       <c r="B48" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D48" s="2"/>
       <c r="E48" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
+      <c r="A49" s="20"/>
       <c r="B49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>108</v>
-      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
+      <c r="A50" s="20" t="s">
+        <v>35</v>
+      </c>
       <c r="B50" s="2" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>106</v>
-      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="2"/>
     </row>
     <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
+      <c r="A51" s="20"/>
       <c r="B51" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="D51" s="2"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="2"/>
+      <c r="E51" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A52" s="20"/>
       <c r="B52" s="2" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="2"/>
+      <c r="E52" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
+      <c r="A53" s="20"/>
       <c r="B53" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>71</v>
@@ -1766,141 +1764,131 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
+      <c r="A54" s="20"/>
       <c r="B54" s="2" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
+      <c r="A55" s="20"/>
       <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
+      <c r="A56" s="20" t="s">
+        <v>27</v>
+      </c>
       <c r="B56" s="2" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>99</v>
-      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="2"/>
     </row>
     <row r="57" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="8"/>
+      <c r="A57" s="20"/>
       <c r="B57" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="2"/>
     </row>
     <row r="58" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="A58" s="20"/>
       <c r="B58" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="2"/>
+      <c r="E58" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="59" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="8"/>
+      <c r="A59" s="20"/>
       <c r="B59" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3"/>
       <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="8"/>
+      <c r="A60" s="20"/>
       <c r="B60" s="2" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="8"/>
+      <c r="A61" s="20"/>
       <c r="B61" s="2" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="3"/>
       <c r="F61" s="2"/>
     </row>
     <row r="62" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="8"/>
+      <c r="A62" s="20"/>
       <c r="B62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="2"/>
     </row>
     <row r="63" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
+      <c r="A63" s="20"/>
       <c r="B63" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>66</v>
@@ -1910,19 +1898,21 @@
       <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
+      <c r="A64" s="20"/>
       <c r="B64" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="D64" s="2"/>
       <c r="E64" s="3"/>
       <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
+      <c r="A65" s="20"/>
       <c r="B65" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>66</v>
@@ -1932,123 +1922,119 @@
       <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
+      <c r="A66" s="20"/>
       <c r="B66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="3"/>
       <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="8"/>
+      <c r="A67" s="20"/>
       <c r="B67" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D67" s="2"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="2"/>
+      <c r="E67" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
+      <c r="A68" s="20"/>
       <c r="B68" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="D68" s="2"/>
       <c r="E68" s="3"/>
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="8"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D69" s="2"/>
-      <c r="E69" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="2"/>
     </row>
     <row r="70" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="8"/>
+      <c r="A70" s="20"/>
       <c r="B70" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="3"/>
       <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="8"/>
+      <c r="A71" s="20"/>
       <c r="B71" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="2"/>
+      <c r="E71" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="8"/>
+      <c r="A72" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="B72" s="2" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3"/>
       <c r="F72" s="2"/>
     </row>
     <row r="73" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="8"/>
+      <c r="A73" s="20"/>
       <c r="B73" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="E73" s="3"/>
+      <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="A74" s="20"/>
       <c r="B74" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="3"/>
       <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="8"/>
+      <c r="A75" s="20"/>
       <c r="B75" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -2056,9 +2042,9 @@
       <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="8"/>
+      <c r="A76" s="20"/>
       <c r="B76" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -2066,9 +2052,9 @@
       <c r="F76" s="2"/>
     </row>
     <row r="77" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="8"/>
+      <c r="A77" s="20"/>
       <c r="B77" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -2076,9 +2062,9 @@
       <c r="F77" s="2"/>
     </row>
     <row r="78" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="8"/>
+      <c r="A78" s="20"/>
       <c r="B78" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -2086,77 +2072,79 @@
       <c r="F78" s="2"/>
     </row>
     <row r="79" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="8"/>
-      <c r="B79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="2"/>
+      <c r="A79" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="9"/>
     </row>
     <row r="80" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="8"/>
+      <c r="A80" s="20" t="s">
+        <v>61</v>
+      </c>
       <c r="B80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="D80" s="2"/>
       <c r="E80" s="3"/>
       <c r="F80" s="2"/>
     </row>
     <row r="81" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="13"/>
+      <c r="A81" s="20"/>
+      <c r="B81" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="2"/>
     </row>
     <row r="82" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="A82" s="20"/>
       <c r="B82" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="3"/>
       <c r="F82" s="2"/>
     </row>
     <row r="83" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="8"/>
+      <c r="A83" s="20"/>
       <c r="B83" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>79</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="3"/>
       <c r="F83" s="2"/>
     </row>
     <row r="84" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="8"/>
+      <c r="A84" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="B84" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>78</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="3"/>
       <c r="F84" s="2"/>
     </row>
     <row r="85" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="8"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -2164,11 +2152,9 @@
       <c r="F85" s="2"/>
     </row>
     <row r="86" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>56</v>
-      </c>
+      <c r="A86" s="22"/>
       <c r="B86" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -2176,9 +2162,9 @@
       <c r="F86" s="2"/>
     </row>
     <row r="87" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="11"/>
+      <c r="A87" s="22"/>
       <c r="B87" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -2186,9 +2172,9 @@
       <c r="F87" s="2"/>
     </row>
     <row r="88" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="11"/>
+      <c r="A88" s="22"/>
       <c r="B88" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -2196,9 +2182,9 @@
       <c r="F88" s="2"/>
     </row>
     <row r="89" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="11"/>
+      <c r="A89" s="22"/>
       <c r="B89" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -2206,19 +2192,21 @@
       <c r="F89" s="2"/>
     </row>
     <row r="90" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="11"/>
+      <c r="A90" s="22"/>
       <c r="B90" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D90" s="2"/>
       <c r="E90" s="3"/>
       <c r="F90" s="2"/>
     </row>
     <row r="91" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="11"/>
+      <c r="A91" s="22"/>
       <c r="B91" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -2226,31 +2214,31 @@
       <c r="F91" s="2"/>
     </row>
     <row r="92" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="11"/>
+      <c r="A92" s="22"/>
       <c r="B92" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="3"/>
       <c r="F92" s="2"/>
     </row>
     <row r="93" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="11"/>
+      <c r="A93" s="22"/>
       <c r="B93" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="D93" s="2"/>
       <c r="E93" s="3"/>
       <c r="F93" s="2"/>
     </row>
     <row r="94" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="11"/>
+      <c r="A94" s="22"/>
       <c r="B94" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -2258,9 +2246,9 @@
       <c r="F94" s="2"/>
     </row>
     <row r="95" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="11"/>
+      <c r="A95" s="22"/>
       <c r="B95" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>76</v>
@@ -2270,9 +2258,9 @@
       <c r="F95" s="2"/>
     </row>
     <row r="96" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="11"/>
+      <c r="A96" s="22"/>
       <c r="B96" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -2280,91 +2268,95 @@
       <c r="F96" s="2"/>
     </row>
     <row r="97" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="11"/>
+      <c r="A97" s="22"/>
       <c r="B97" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="3"/>
       <c r="F97" s="2"/>
     </row>
     <row r="98" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="11"/>
+      <c r="A98" s="23"/>
       <c r="B98" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="D98" s="2"/>
       <c r="E98" s="3"/>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="11"/>
+    <row r="99" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="20" t="s">
+        <v>40</v>
+      </c>
       <c r="B99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="3"/>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="10"/>
+    <row r="100" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="20"/>
       <c r="B100" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="3"/>
       <c r="F100" s="2"/>
     </row>
     <row r="101" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="8" t="s">
-        <v>40</v>
-      </c>
+      <c r="A101" s="20"/>
       <c r="B101" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D101" s="2"/>
       <c r="E101" s="3"/>
       <c r="F101" s="2"/>
     </row>
-    <row r="102" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="8"/>
+    <row r="102" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="20" t="s">
+        <v>35</v>
+      </c>
       <c r="B102" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="D102" s="2"/>
       <c r="E102" s="3"/>
       <c r="F102" s="2"/>
     </row>
-    <row r="103" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="8"/>
+    <row r="103" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="20"/>
       <c r="B103" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="3"/>
-      <c r="F103" s="2"/>
+      <c r="F103" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="104" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A104" s="20"/>
       <c r="B104" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>71</v>
@@ -2374,47 +2366,45 @@
       <c r="F104" s="2"/>
     </row>
     <row r="105" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="8"/>
+      <c r="A105" s="20"/>
       <c r="B105" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="3"/>
-      <c r="F105" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F105" s="2"/>
     </row>
     <row r="106" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="8"/>
+      <c r="A106" s="20"/>
       <c r="B106" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="3"/>
       <c r="F106" s="2"/>
     </row>
     <row r="107" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="8"/>
+      <c r="A107" s="20"/>
       <c r="B107" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="3"/>
       <c r="F107" s="2"/>
     </row>
     <row r="108" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="8"/>
+      <c r="A108" s="20" t="s">
+        <v>27</v>
+      </c>
       <c r="B108" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -2422,23 +2412,21 @@
       <c r="F108" s="2"/>
     </row>
     <row r="109" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="8"/>
+      <c r="A109" s="20"/>
       <c r="B109" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="3"/>
       <c r="F109" s="2"/>
     </row>
     <row r="110" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="A110" s="20"/>
       <c r="B110" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -2446,43 +2434,43 @@
       <c r="F110" s="2"/>
     </row>
     <row r="111" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="8"/>
+      <c r="A111" s="20"/>
       <c r="B111" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="3"/>
       <c r="F111" s="2"/>
     </row>
     <row r="112" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="8"/>
+      <c r="A112" s="20"/>
       <c r="B112" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C112" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="D112" s="2"/>
       <c r="E112" s="3"/>
       <c r="F112" s="2"/>
     </row>
     <row r="113" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="8"/>
+      <c r="A113" s="20"/>
       <c r="B113" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="3"/>
       <c r="F113" s="2"/>
     </row>
     <row r="114" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="8"/>
+      <c r="A114" s="20"/>
       <c r="B114" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>66</v>
@@ -2492,19 +2480,21 @@
       <c r="F114" s="2"/>
     </row>
     <row r="115" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="8"/>
+      <c r="A115" s="20"/>
       <c r="B115" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C115" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="D115" s="2"/>
       <c r="E115" s="3"/>
       <c r="F115" s="2"/>
     </row>
     <row r="116" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="8"/>
+      <c r="A116" s="20"/>
       <c r="B116" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>66</v>
@@ -2514,21 +2504,18 @@
       <c r="F116" s="2"/>
     </row>
     <row r="117" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="8"/>
+      <c r="A117" s="20"/>
       <c r="B117" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="3"/>
       <c r="F117" s="2"/>
     </row>
     <row r="118" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="8"/>
+      <c r="A118" s="20"/>
       <c r="B118" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>66</v>
@@ -2538,65 +2525,66 @@
       <c r="F118" s="2"/>
     </row>
     <row r="119" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="8"/>
+      <c r="A119" s="20"/>
       <c r="B119" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="D119" s="2"/>
+      <c r="E119" s="3"/>
       <c r="F119" s="2"/>
     </row>
     <row r="120" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="8"/>
+      <c r="A120" s="20"/>
       <c r="B120" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" s="3"/>
       <c r="F120" s="2"/>
     </row>
     <row r="121" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="8"/>
+      <c r="A121" s="20"/>
       <c r="B121" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D121" s="2"/>
-      <c r="E121" s="3"/>
       <c r="F121" s="2"/>
     </row>
     <row r="122" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="8"/>
+      <c r="A122" s="20"/>
       <c r="B122" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="3"/>
       <c r="F122" s="2"/>
     </row>
     <row r="123" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="8"/>
+      <c r="A123" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="B123" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>63</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C123" s="2"/>
       <c r="D123" s="2"/>
+      <c r="E123" s="3"/>
       <c r="F123" s="2"/>
     </row>
     <row r="124" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="8"/>
+      <c r="A124" s="20"/>
       <c r="B124" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -2604,11 +2592,9 @@
       <c r="F124" s="2"/>
     </row>
     <row r="125" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="A125" s="20"/>
       <c r="B125" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -2616,9 +2602,9 @@
       <c r="F125" s="2"/>
     </row>
     <row r="126" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="8"/>
+      <c r="A126" s="20"/>
       <c r="B126" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -2626,9 +2612,9 @@
       <c r="F126" s="2"/>
     </row>
     <row r="127" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="8"/>
+      <c r="A127" s="20"/>
       <c r="B127" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -2636,9 +2622,9 @@
       <c r="F127" s="2"/>
     </row>
     <row r="128" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="8"/>
+      <c r="A128" s="20"/>
       <c r="B128" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -2646,41 +2632,45 @@
       <c r="F128" s="2"/>
     </row>
     <row r="129" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="8"/>
-      <c r="B129" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="2"/>
+      <c r="A129" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="10"/>
+      <c r="F129" s="9"/>
     </row>
     <row r="130" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="8"/>
+      <c r="A130" s="20" t="s">
+        <v>61</v>
+      </c>
       <c r="B130" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="D130" s="2"/>
       <c r="E130" s="3"/>
       <c r="F130" s="2"/>
     </row>
     <row r="131" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B131" s="13"/>
-      <c r="C131" s="13"/>
-      <c r="D131" s="13"/>
-      <c r="E131" s="14"/>
-      <c r="F131" s="13"/>
+      <c r="A131" s="20"/>
+      <c r="B131" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D131" s="2"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="2"/>
     </row>
     <row r="132" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="A132" s="20"/>
       <c r="B132" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>4</v>
@@ -2690,9 +2680,9 @@
       <c r="F132" s="2"/>
     </row>
     <row r="133" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="8"/>
+      <c r="A133" s="20"/>
       <c r="B133" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>4</v>
@@ -2702,9 +2692,11 @@
       <c r="F133" s="2"/>
     </row>
     <row r="134" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="8"/>
+      <c r="A134" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="B134" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>4</v>
@@ -2714,9 +2706,9 @@
       <c r="F134" s="2"/>
     </row>
     <row r="135" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="8"/>
+      <c r="A135" s="22"/>
       <c r="B135" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>4</v>
@@ -2726,11 +2718,9 @@
       <c r="F135" s="2"/>
     </row>
     <row r="136" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="12" t="s">
-        <v>56</v>
-      </c>
+      <c r="A136" s="22"/>
       <c r="B136" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>4</v>
@@ -2740,9 +2730,9 @@
       <c r="F136" s="2"/>
     </row>
     <row r="137" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="11"/>
+      <c r="A137" s="22"/>
       <c r="B137" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>4</v>
@@ -2752,9 +2742,9 @@
       <c r="F137" s="2"/>
     </row>
     <row r="138" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="11"/>
+      <c r="A138" s="22"/>
       <c r="B138" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>4</v>
@@ -2764,9 +2754,9 @@
       <c r="F138" s="2"/>
     </row>
     <row r="139" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="11"/>
+      <c r="A139" s="22"/>
       <c r="B139" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>4</v>
@@ -2776,9 +2766,9 @@
       <c r="F139" s="2"/>
     </row>
     <row r="140" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="11"/>
+      <c r="A140" s="22"/>
       <c r="B140" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>4</v>
@@ -2788,9 +2778,9 @@
       <c r="F140" s="2"/>
     </row>
     <row r="141" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="11"/>
+      <c r="A141" s="22"/>
       <c r="B141" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>4</v>
@@ -2800,9 +2790,9 @@
       <c r="F141" s="2"/>
     </row>
     <row r="142" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="11"/>
+      <c r="A142" s="22"/>
       <c r="B142" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>4</v>
@@ -2812,9 +2802,9 @@
       <c r="F142" s="2"/>
     </row>
     <row r="143" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="11"/>
+      <c r="A143" s="22"/>
       <c r="B143" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>4</v>
@@ -2824,9 +2814,9 @@
       <c r="F143" s="2"/>
     </row>
     <row r="144" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="11"/>
+      <c r="A144" s="22"/>
       <c r="B144" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>4</v>
@@ -2836,9 +2826,9 @@
       <c r="F144" s="2"/>
     </row>
     <row r="145" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="11"/>
+      <c r="A145" s="22"/>
       <c r="B145" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>4</v>
@@ -2848,9 +2838,9 @@
       <c r="F145" s="2"/>
     </row>
     <row r="146" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="11"/>
+      <c r="A146" s="22"/>
       <c r="B146" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>4</v>
@@ -2860,9 +2850,9 @@
       <c r="F146" s="2"/>
     </row>
     <row r="147" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="11"/>
+      <c r="A147" s="22"/>
       <c r="B147" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>4</v>
@@ -2872,9 +2862,9 @@
       <c r="F147" s="2"/>
     </row>
     <row r="148" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="11"/>
+      <c r="A148" s="23"/>
       <c r="B148" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>4</v>
@@ -2883,36 +2873,36 @@
       <c r="E148" s="3"/>
       <c r="F148" s="2"/>
     </row>
-    <row r="149" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="11"/>
-      <c r="B149" s="2" t="s">
-        <v>42</v>
+    <row r="149" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" s="3"/>
       <c r="F149" s="2"/>
     </row>
-    <row r="150" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="10"/>
-      <c r="B150" s="2" t="s">
-        <v>41</v>
+    <row r="150" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="20"/>
+      <c r="B150" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" s="3"/>
       <c r="F150" s="2"/>
     </row>
     <row r="151" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B151" s="9" t="s">
-        <v>39</v>
+      <c r="A151" s="20"/>
+      <c r="B151" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>36</v>
@@ -2921,36 +2911,38 @@
       <c r="E151" s="3"/>
       <c r="F151" s="2"/>
     </row>
-    <row r="152" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="8"/>
-      <c r="B152" s="9" t="s">
-        <v>38</v>
+    <row r="152" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" s="3"/>
       <c r="F152" s="2"/>
     </row>
-    <row r="153" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="8"/>
-      <c r="B153" s="9" t="s">
-        <v>37</v>
+    <row r="153" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="20"/>
+      <c r="B153" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" s="3"/>
-      <c r="F153" s="2"/>
+      <c r="F153" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="154" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A154" s="20"/>
       <c r="B154" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>4</v>
@@ -2960,23 +2952,21 @@
       <c r="F154" s="2"/>
     </row>
     <row r="155" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="8"/>
+      <c r="A155" s="20"/>
       <c r="B155" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="3"/>
-      <c r="F155" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F155" s="2"/>
     </row>
     <row r="156" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="8"/>
+      <c r="A156" s="20"/>
       <c r="B156" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>4</v>
@@ -2986,9 +2976,9 @@
       <c r="F156" s="2"/>
     </row>
     <row r="157" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="8"/>
+      <c r="A157" s="20"/>
       <c r="B157" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>4</v>
@@ -2998,9 +2988,11 @@
       <c r="F157" s="2"/>
     </row>
     <row r="158" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="8"/>
+      <c r="A158" s="20" t="s">
+        <v>27</v>
+      </c>
       <c r="B158" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>4</v>
@@ -3010,9 +3002,9 @@
       <c r="F158" s="2"/>
     </row>
     <row r="159" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="8"/>
+      <c r="A159" s="20"/>
       <c r="B159" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>4</v>
@@ -3022,11 +3014,9 @@
       <c r="F159" s="2"/>
     </row>
     <row r="160" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="A160" s="20"/>
       <c r="B160" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>4</v>
@@ -3036,9 +3026,9 @@
       <c r="F160" s="2"/>
     </row>
     <row r="161" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="8"/>
+      <c r="A161" s="20"/>
       <c r="B161" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>4</v>
@@ -3048,9 +3038,9 @@
       <c r="F161" s="2"/>
     </row>
     <row r="162" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="8"/>
+      <c r="A162" s="20"/>
       <c r="B162" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>4</v>
@@ -3060,9 +3050,9 @@
       <c r="F162" s="2"/>
     </row>
     <row r="163" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="8"/>
+      <c r="A163" s="20"/>
       <c r="B163" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>4</v>
@@ -3072,9 +3062,9 @@
       <c r="F163" s="2"/>
     </row>
     <row r="164" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="8"/>
+      <c r="A164" s="20"/>
       <c r="B164" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>4</v>
@@ -3084,9 +3074,9 @@
       <c r="F164" s="2"/>
     </row>
     <row r="165" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="8"/>
+      <c r="A165" s="20"/>
       <c r="B165" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>4</v>
@@ -3096,9 +3086,9 @@
       <c r="F165" s="2"/>
     </row>
     <row r="166" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="8"/>
+      <c r="A166" s="20"/>
       <c r="B166" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>4</v>
@@ -3108,21 +3098,20 @@
       <c r="F166" s="2"/>
     </row>
     <row r="167" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="8"/>
+      <c r="A167" s="20"/>
       <c r="B167" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D167" s="2"/>
-      <c r="E167" s="3"/>
       <c r="F167" s="2"/>
     </row>
     <row r="168" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="8"/>
+      <c r="A168" s="20"/>
       <c r="B168" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>4</v>
@@ -3132,20 +3121,21 @@
       <c r="F168" s="2"/>
     </row>
     <row r="169" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="8"/>
+      <c r="A169" s="20"/>
       <c r="B169" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D169" s="2"/>
+      <c r="E169" s="3"/>
       <c r="F169" s="2"/>
     </row>
     <row r="170" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="8"/>
+      <c r="A170" s="20"/>
       <c r="B170" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>4</v>
@@ -3155,21 +3145,20 @@
       <c r="F170" s="2"/>
     </row>
     <row r="171" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="8"/>
+      <c r="A171" s="20"/>
       <c r="B171" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D171" s="2"/>
-      <c r="E171" s="3"/>
       <c r="F171" s="2"/>
     </row>
     <row r="172" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="8"/>
+      <c r="A172" s="20"/>
       <c r="B172" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>4</v>
@@ -3179,20 +3168,23 @@
       <c r="F172" s="2"/>
     </row>
     <row r="173" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="8"/>
+      <c r="A173" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="B173" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D173" s="2"/>
+      <c r="E173" s="3"/>
       <c r="F173" s="2"/>
     </row>
     <row r="174" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="8"/>
+      <c r="A174" s="20"/>
       <c r="B174" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>4</v>
@@ -3202,11 +3194,9 @@
       <c r="F174" s="2"/>
     </row>
     <row r="175" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="A175" s="20"/>
       <c r="B175" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>4</v>
@@ -3216,9 +3206,9 @@
       <c r="F175" s="2"/>
     </row>
     <row r="176" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="8"/>
+      <c r="A176" s="20"/>
       <c r="B176" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>4</v>
@@ -3228,9 +3218,9 @@
       <c r="F176" s="2"/>
     </row>
     <row r="177" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="8"/>
+      <c r="A177" s="20"/>
       <c r="B177" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>4</v>
@@ -3240,9 +3230,9 @@
       <c r="F177" s="2"/>
     </row>
     <row r="178" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="8"/>
+      <c r="A178" s="20"/>
       <c r="B178" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>4</v>
@@ -3252,78 +3242,53 @@
       <c r="F178" s="2"/>
     </row>
     <row r="179" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="8"/>
-      <c r="B179" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D179" s="2"/>
-      <c r="E179" s="3"/>
-      <c r="F179" s="2"/>
+      <c r="A179" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B179" s="5"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="5"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="5"/>
     </row>
     <row r="180" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="8"/>
+      <c r="A180" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="B180" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D180" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="E180" s="3"/>
       <c r="F180" s="2"/>
     </row>
-    <row r="181" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="5"/>
-    </row>
-    <row r="182" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E182" s="3"/>
-      <c r="F182" s="2"/>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="1"/>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:A22"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A46"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="A160:A174"/>
-    <mergeCell ref="A175:A180"/>
-    <mergeCell ref="A110:A124"/>
-    <mergeCell ref="A125:A130"/>
-    <mergeCell ref="A132:A135"/>
-    <mergeCell ref="A136:A150"/>
-    <mergeCell ref="A151:A153"/>
-    <mergeCell ref="A154:A159"/>
+  <mergeCells count="19">
+    <mergeCell ref="A99:A101"/>
+    <mergeCell ref="A102:A107"/>
+    <mergeCell ref="A158:A172"/>
+    <mergeCell ref="A173:A178"/>
+    <mergeCell ref="A108:A122"/>
+    <mergeCell ref="A123:A128"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A134:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A157"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="A72:A78"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A84:A98"/>
+    <mergeCell ref="A2:A20"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A44"/>
+    <mergeCell ref="A45:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
